--- a/clr-cld.xlsx
+++ b/clr-cld.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20625" windowHeight="12735"/>
+    <workbookView windowWidth="27810" windowHeight="10980"/>
   </bookViews>
   <sheets>
     <sheet name="img" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>clr-cld</t>
   </si>
@@ -113,6 +113,18 @@
   </si>
   <si>
     <t>視頻-聖樂-2607230-1.mp4</t>
+  </si>
+  <si>
+    <t>Jesus your my everything</t>
+  </si>
+  <si>
+    <t>&lt;iframe width="464" height="824" src="https://www.youtube.com/embed/LWpHwCx0H6c" title="Jesus your my everything #subscribe #everyone #worship #ofwlife" frameborder="0" allow="accelerometer; autoplay; clipboard-write; encrypted-media; gyroscope; picture-in-picture; web-share" referrerpolicy="strict-origin-when-cross-origin" allowfullscreen&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/LWpHwCx0H6c</t>
+  </si>
+  <si>
+    <t>Youtube</t>
   </si>
 </sst>
 </file>
@@ -1345,15 +1357,29 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="2:9">
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+    <row r="12" s="1" customFormat="1" ht="36" customHeight="1" spans="2:9">
+      <c r="B12" s="7">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7">
+        <v>202600805</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>30</v>
+      </c>
       <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="2:9">
       <c r="B13" s="7"/>
@@ -1460,6 +1486,7 @@
     <hyperlink ref="F9" r:id="rId1" display="https://www.youtube.com/shorts/O89n43UIgD8"/>
     <hyperlink ref="F10" r:id="rId2" display="https://www.youtube.com/shorts/zZ6IB1bYkJE"/>
     <hyperlink ref="F11" r:id="rId3" display="https://www.youtube.com/shorts/WpRmdVipCIc"/>
+    <hyperlink ref="F12" r:id="rId4" display="https://www.youtube.com/shorts/LWpHwCx0H6c"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/clr-cld.xlsx
+++ b/clr-cld.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t>clr-cld</t>
   </si>
@@ -125,6 +125,33 @@
   </si>
   <si>
     <t>Youtube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Have Found A Freind In Jesus very heart touching </t>
+  </si>
+  <si>
+    <t>&lt;iframe width="464" height="824" src="https://www.youtube.com/embed/73DYZjRk9iU" title="I Have Found A Freind In Jesus very heart touching song/cover) Short video| No Reupload" frameborder="0" allow="accelerometer; autoplay; clipboard-write; encrypted-media; gyroscope; picture-in-picture; web-share" referrerpolicy="strict-origin-when-cross-origin" allowfullscreen&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/73DYZjRk9iU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass Me Not, O Gentle Savior | Reggae Gospel </t>
+  </si>
+  <si>
+    <t>&lt;iframe width="573" height="824" src="https://www.youtube.com/embed/691QXMMPglc" title="Pass Me Not, O Gentle Savior | Reggae Gospel Worship Hymn" frameborder="0" allow="accelerometer; autoplay; clipboard-write; encrypted-media; gyroscope; picture-in-picture; web-share" referrerpolicy="strict-origin-when-cross-origin" allowfullscreen&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/691QXMMPglc</t>
+  </si>
+  <si>
+    <t>O Lord My God (How Great Thou Art) | Soul-Stirring</t>
+  </si>
+  <si>
+    <t>&lt;iframe width="491" height="824" src="https://www.youtube.com/embed/jUoksm45fK8" title="O Lord My God (How Great Thou Art) | Soul-Stirring Worship Hymn" frameborder="0" allow="accelerometer; autoplay; clipboard-write; encrypted-media; gyroscope; picture-in-picture; web-share" referrerpolicy="strict-origin-when-cross-origin" allowfullscreen&gt;&lt;/iframe&gt;</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/jUoksm45fK8</t>
   </si>
 </sst>
 </file>
@@ -137,7 +164,7 @@
     <numFmt numFmtId="176" formatCode="_-&quot;NT$&quot;* #,##0.00_-;\-&quot;NT$&quot;* #,##0.00_-;_-&quot;NT$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;NT$&quot;* #,##0_-;\-&quot;NT$&quot;* #,##0_-;_-&quot;NT$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,6 +198,13 @@
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0F0F0F"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -689,137 +723,137 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -855,6 +889,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1381,32 +1418,70 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="2:9">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+    <row r="13" s="1" customFormat="1" ht="93" customHeight="1" spans="2:9">
+      <c r="B13" s="7">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7">
+        <v>202600807</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>34</v>
+      </c>
       <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="2:9">
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="94" customHeight="1" spans="2:9">
+      <c r="B14" s="7">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>202600807</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>37</v>
+      </c>
       <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="2:9">
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="189.75" spans="2:9">
+      <c r="B15" s="7">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>202600807</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -1487,6 +1562,9 @@
     <hyperlink ref="F10" r:id="rId2" display="https://www.youtube.com/shorts/zZ6IB1bYkJE"/>
     <hyperlink ref="F11" r:id="rId3" display="https://www.youtube.com/shorts/WpRmdVipCIc"/>
     <hyperlink ref="F12" r:id="rId4" display="https://www.youtube.com/shorts/LWpHwCx0H6c"/>
+    <hyperlink ref="F13" r:id="rId5" display="https://www.youtube.com/shorts/73DYZjRk9iU"/>
+    <hyperlink ref="F14" r:id="rId6" display="https://www.youtube.com/shorts/691QXMMPglc"/>
+    <hyperlink ref="F15" r:id="rId7" display="https://www.youtube.com/shorts/jUoksm45fK8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
